--- a/daily_matches/job_matches_2026-06-28.xlsx
+++ b/daily_matches/job_matches_2026-06-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer (Business Analyst IV)</t>
+          <t>Google Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fairfax County Government</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, BigQuery, Data Lake, Apache Airflow, Snowflake, BigQuery, Hadoop, PostgreSQL</t>
+          <t>RAG, Prompt Engineering, TensorFlow, XGBoost, BigQuery, CI/CD, Jenkins, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414e38f5ca1fe7f7</t>
+          <t>https://www.indeed.com/viewjob?jk=063d41992d4b3402</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prin Software Engineer - AFS</t>
+          <t>Sr Full Stack Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Metropolitan Council of the Twin Cities</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, S3, Docker, Kubernetes, AKS, CI/CD, Terraform, Git</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, MySQL, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4459c55264602070</t>
+          <t>https://www.indeed.com/viewjob?jk=9b55caa3b9d44424</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb8fea85a87bab5</t>
+          <t>https://www.indeed.com/viewjob?jk=6df027064a5f894b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Associated Press</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, EC2, FastAPI, Kubernetes, CI/CD, Terraform</t>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d45b8d8fdc6454d</t>
+          <t>https://www.indeed.com/viewjob?jk=bb5e568a25691ba4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, US Production</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zafran Security</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,147 +636,42 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3c0d8531de480d</t>
+          <t>https://www.indeed.com/viewjob?jk=db7a99827b79188f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
+          <t>Senior Application Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Major League Baseball (MLB)</t>
+          <t>City of Rockville</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gemini, BigQuery, Dataflow, CI/CD, Terraform, Git, BigQuery, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae4dfa2efb93cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Full-Stack AI Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Krem.Energy</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>East Rutherford, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a89dad20b03f4f19</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>NiCE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sandy, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>S3, EC2, Kinesis, Docker, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13889fd2bd869acd</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Machine Learning Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>The Associated Press</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, R, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8d4080714a0b2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffba52098259ac2</t>
         </is>
       </c>
     </row>
